--- a/output/graficos_dimensiones/comunal_e_preneta_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2022_metropolitana.xlsx
@@ -147,51 +147,51 @@
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peñaflor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:51</t>
+    <t xml:space="preserve">2026-09-09 23:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1260,7 +1260,7 @@
         <v>43</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>13122</v>
+        <v>13119</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -1286,7 +1286,7 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13113</v>
+        <v>13120</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -1299,7 +1299,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13301</v>
+        <v>13113</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1312,7 +1312,7 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13201</v>
+        <v>13301</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -1325,7 +1325,7 @@
         <v>48</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>13107</v>
+        <v>13124</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
@@ -1338,7 +1338,7 @@
         <v>49</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>13132</v>
+        <v>13107</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
@@ -1351,7 +1351,7 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>13114</v>
+        <v>13201</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
@@ -1364,7 +1364,7 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13115</v>
+        <v>13132</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -1377,7 +1377,7 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13119</v>
+        <v>13125</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -1390,7 +1390,7 @@
         <v>53</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>13120</v>
+        <v>13605</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1403,7 +1403,7 @@
         <v>54</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>13124</v>
+        <v>13115</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>13125</v>
+        <v>13303</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -1429,7 +1429,7 @@
         <v>56</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>13605</v>
+        <v>13114</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -1442,7 +1442,7 @@
         <v>57</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>13303</v>
+        <v>13122</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_preneta_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_preneta_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:52</t>
+    <t xml:space="preserve">2026-09-18 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
